--- a/results/期货库存明细.xlsx
+++ b/results/期货库存明细.xlsx
@@ -367,7 +367,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="50">
+  <fills count="51">
     <fill>
       <patternFill/>
     </fill>
@@ -662,6 +662,12 @@
         <bgColor rgb="00FF0000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+        <bgColor rgb="00FFFF00"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="12">
     <border>
@@ -953,7 +959,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1313,6 +1319,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="50" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -6656,7 +6663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X22"/>
+  <dimension ref="A1:X76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8670,6 +8677,5190 @@
       </c>
       <c r="W22" s="123" t="n"/>
       <c r="X22" s="123" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B23" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C23" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D23" s="125" t="inlineStr">
+        <is>
+          <t>6H1035A00</t>
+        </is>
+      </c>
+      <c r="E23" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F23" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G23" s="125" t="n">
+        <v>1180</v>
+      </c>
+      <c r="H23" s="125" t="n">
+        <v>5515</v>
+      </c>
+      <c r="I23" s="125" t="n">
+        <v>5555</v>
+      </c>
+      <c r="J23" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K23" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L23" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M23" s="125" t="inlineStr"/>
+      <c r="N23" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/9</t>
+        </is>
+      </c>
+      <c r="O23" s="125" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="P23" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q23" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R23" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S23" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U23" s="125" t="inlineStr"/>
+      <c r="V23" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W23" s="125" t="inlineStr"/>
+      <c r="X23" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B24" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C24" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D24" s="125" t="inlineStr">
+        <is>
+          <t>6H1035B00</t>
+        </is>
+      </c>
+      <c r="E24" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F24" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G24" s="125" t="n">
+        <v>1180</v>
+      </c>
+      <c r="H24" s="125" t="n">
+        <v>5490</v>
+      </c>
+      <c r="I24" s="125" t="n">
+        <v>5530</v>
+      </c>
+      <c r="J24" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K24" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L24" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M24" s="125" t="inlineStr"/>
+      <c r="N24" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/9</t>
+        </is>
+      </c>
+      <c r="O24" s="125" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="P24" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q24" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R24" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S24" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U24" s="125" t="inlineStr"/>
+      <c r="V24" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W24" s="125" t="inlineStr"/>
+      <c r="X24" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B25" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C25" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D25" s="125" t="inlineStr">
+        <is>
+          <t>6H1035C00</t>
+        </is>
+      </c>
+      <c r="E25" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F25" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G25" s="125" t="n">
+        <v>1180</v>
+      </c>
+      <c r="H25" s="125" t="n">
+        <v>5490</v>
+      </c>
+      <c r="I25" s="125" t="n">
+        <v>5530</v>
+      </c>
+      <c r="J25" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K25" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L25" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M25" s="125" t="inlineStr"/>
+      <c r="N25" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/9</t>
+        </is>
+      </c>
+      <c r="O25" s="125" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="P25" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q25" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R25" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S25" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U25" s="125" t="inlineStr"/>
+      <c r="V25" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W25" s="125" t="inlineStr"/>
+      <c r="X25" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B26" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C26" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D26" s="125" t="inlineStr">
+        <is>
+          <t>6H1037A00</t>
+        </is>
+      </c>
+      <c r="E26" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F26" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G26" s="125" t="n">
+        <v>1100</v>
+      </c>
+      <c r="H26" s="125" t="n">
+        <v>5130</v>
+      </c>
+      <c r="I26" s="125" t="n">
+        <v>5170</v>
+      </c>
+      <c r="J26" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K26" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L26" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M26" s="125" t="inlineStr"/>
+      <c r="N26" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/9</t>
+        </is>
+      </c>
+      <c r="O26" s="125" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="P26" s="125" t="n">
+        <v>1202</v>
+      </c>
+      <c r="Q26" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R26" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S26" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U26" s="125" t="inlineStr"/>
+      <c r="V26" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W26" s="125" t="inlineStr"/>
+      <c r="X26" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B27" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C27" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D27" s="125" t="inlineStr">
+        <is>
+          <t>6H1037D00</t>
+        </is>
+      </c>
+      <c r="E27" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F27" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G27" s="125" t="n">
+        <v>1304</v>
+      </c>
+      <c r="H27" s="125" t="n">
+        <v>6035</v>
+      </c>
+      <c r="I27" s="125" t="n">
+        <v>6075</v>
+      </c>
+      <c r="J27" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K27" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L27" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M27" s="125" t="inlineStr"/>
+      <c r="N27" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/10</t>
+        </is>
+      </c>
+      <c r="O27" s="125" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="P27" s="125" t="n">
+        <v>1202</v>
+      </c>
+      <c r="Q27" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R27" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S27" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U27" s="125" t="inlineStr"/>
+      <c r="V27" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W27" s="125" t="inlineStr"/>
+      <c r="X27" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B28" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C28" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D28" s="125" t="inlineStr">
+        <is>
+          <t>6H1039D00</t>
+        </is>
+      </c>
+      <c r="E28" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F28" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G28" s="125" t="n">
+        <v>1180</v>
+      </c>
+      <c r="H28" s="125" t="n">
+        <v>5425</v>
+      </c>
+      <c r="I28" s="125" t="n">
+        <v>5465</v>
+      </c>
+      <c r="J28" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K28" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L28" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M28" s="125" t="inlineStr"/>
+      <c r="N28" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/9</t>
+        </is>
+      </c>
+      <c r="O28" s="125" t="n">
+        <v>0.528</v>
+      </c>
+      <c r="P28" s="125" t="n">
+        <v>1202</v>
+      </c>
+      <c r="Q28" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R28" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S28" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U28" s="125" t="inlineStr"/>
+      <c r="V28" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W28" s="125" t="inlineStr"/>
+      <c r="X28" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B29" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C29" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D29" s="125" t="inlineStr">
+        <is>
+          <t>6H1047A00</t>
+        </is>
+      </c>
+      <c r="E29" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F29" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G29" s="125" t="n">
+        <v>950</v>
+      </c>
+      <c r="H29" s="125" t="n">
+        <v>4440</v>
+      </c>
+      <c r="I29" s="125" t="n">
+        <v>4480</v>
+      </c>
+      <c r="J29" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K29" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L29" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M29" s="125" t="inlineStr"/>
+      <c r="N29" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/9</t>
+        </is>
+      </c>
+      <c r="O29" s="125" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="P29" s="125" t="n">
+        <v>1202</v>
+      </c>
+      <c r="Q29" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R29" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S29" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U29" s="125" t="inlineStr"/>
+      <c r="V29" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W29" s="125" t="inlineStr"/>
+      <c r="X29" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B30" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C30" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D30" s="125" t="inlineStr">
+        <is>
+          <t>6H1047C00</t>
+        </is>
+      </c>
+      <c r="E30" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F30" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G30" s="125" t="n">
+        <v>950</v>
+      </c>
+      <c r="H30" s="125" t="n">
+        <v>4425</v>
+      </c>
+      <c r="I30" s="125" t="n">
+        <v>4465</v>
+      </c>
+      <c r="J30" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K30" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L30" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M30" s="125" t="inlineStr"/>
+      <c r="N30" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/10</t>
+        </is>
+      </c>
+      <c r="O30" s="125" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="P30" s="125" t="n">
+        <v>1202</v>
+      </c>
+      <c r="Q30" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R30" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S30" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U30" s="125" t="inlineStr"/>
+      <c r="V30" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W30" s="125" t="inlineStr"/>
+      <c r="X30" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B31" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C31" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D31" s="125" t="inlineStr">
+        <is>
+          <t>6H1047D00</t>
+        </is>
+      </c>
+      <c r="E31" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F31" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G31" s="125" t="n">
+        <v>950</v>
+      </c>
+      <c r="H31" s="125" t="n">
+        <v>4420</v>
+      </c>
+      <c r="I31" s="125" t="n">
+        <v>4460</v>
+      </c>
+      <c r="J31" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K31" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L31" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M31" s="125" t="inlineStr"/>
+      <c r="N31" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/10</t>
+        </is>
+      </c>
+      <c r="O31" s="125" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="P31" s="125" t="n">
+        <v>1202</v>
+      </c>
+      <c r="Q31" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R31" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S31" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U31" s="125" t="inlineStr"/>
+      <c r="V31" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W31" s="125" t="inlineStr"/>
+      <c r="X31" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B32" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C32" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D32" s="125" t="inlineStr">
+        <is>
+          <t>6H1047E00</t>
+        </is>
+      </c>
+      <c r="E32" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F32" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G32" s="125" t="n">
+        <v>930</v>
+      </c>
+      <c r="H32" s="125" t="n">
+        <v>4310</v>
+      </c>
+      <c r="I32" s="125" t="n">
+        <v>4350</v>
+      </c>
+      <c r="J32" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K32" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L32" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M32" s="125" t="inlineStr"/>
+      <c r="N32" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/9</t>
+        </is>
+      </c>
+      <c r="O32" s="125" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="P32" s="125" t="n">
+        <v>1202</v>
+      </c>
+      <c r="Q32" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R32" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S32" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U32" s="125" t="inlineStr"/>
+      <c r="V32" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W32" s="125" t="inlineStr"/>
+      <c r="X32" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B33" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C33" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D33" s="125" t="inlineStr">
+        <is>
+          <t>6H1052A00</t>
+        </is>
+      </c>
+      <c r="E33" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F33" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G33" s="125" t="n">
+        <v>950</v>
+      </c>
+      <c r="H33" s="125" t="n">
+        <v>4440</v>
+      </c>
+      <c r="I33" s="125" t="n">
+        <v>4480</v>
+      </c>
+      <c r="J33" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K33" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L33" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M33" s="125" t="inlineStr"/>
+      <c r="N33" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/10</t>
+        </is>
+      </c>
+      <c r="O33" s="125" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="P33" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q33" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R33" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S33" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U33" s="125" t="inlineStr"/>
+      <c r="V33" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W33" s="125" t="inlineStr"/>
+      <c r="X33" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B34" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C34" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D34" s="125" t="inlineStr">
+        <is>
+          <t>6H1052B00</t>
+        </is>
+      </c>
+      <c r="E34" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F34" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G34" s="125" t="n">
+        <v>950</v>
+      </c>
+      <c r="H34" s="125" t="n">
+        <v>4425</v>
+      </c>
+      <c r="I34" s="125" t="n">
+        <v>4465</v>
+      </c>
+      <c r="J34" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K34" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L34" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M34" s="125" t="inlineStr"/>
+      <c r="N34" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/9</t>
+        </is>
+      </c>
+      <c r="O34" s="125" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="P34" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q34" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R34" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S34" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U34" s="125" t="inlineStr"/>
+      <c r="V34" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W34" s="125" t="inlineStr"/>
+      <c r="X34" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B35" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C35" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D35" s="125" t="inlineStr">
+        <is>
+          <t>6H1052C00</t>
+        </is>
+      </c>
+      <c r="E35" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F35" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G35" s="125" t="n">
+        <v>950</v>
+      </c>
+      <c r="H35" s="125" t="n">
+        <v>4410</v>
+      </c>
+      <c r="I35" s="125" t="n">
+        <v>4450</v>
+      </c>
+      <c r="J35" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K35" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L35" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M35" s="125" t="inlineStr"/>
+      <c r="N35" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/9</t>
+        </is>
+      </c>
+      <c r="O35" s="125" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="P35" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q35" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R35" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S35" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U35" s="125" t="inlineStr"/>
+      <c r="V35" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W35" s="125" t="inlineStr"/>
+      <c r="X35" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B36" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C36" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D36" s="125" t="inlineStr">
+        <is>
+          <t>6H1052D00</t>
+        </is>
+      </c>
+      <c r="E36" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F36" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G36" s="125" t="n">
+        <v>950</v>
+      </c>
+      <c r="H36" s="125" t="n">
+        <v>4420</v>
+      </c>
+      <c r="I36" s="125" t="n">
+        <v>4460</v>
+      </c>
+      <c r="J36" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K36" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L36" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M36" s="125" t="inlineStr"/>
+      <c r="N36" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/9</t>
+        </is>
+      </c>
+      <c r="O36" s="125" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="P36" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q36" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R36" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S36" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U36" s="125" t="inlineStr"/>
+      <c r="V36" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W36" s="125" t="inlineStr"/>
+      <c r="X36" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B37" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C37" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D37" s="125" t="inlineStr">
+        <is>
+          <t>6H1052E00</t>
+        </is>
+      </c>
+      <c r="E37" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F37" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G37" s="125" t="n">
+        <v>928</v>
+      </c>
+      <c r="H37" s="125" t="n">
+        <v>4280</v>
+      </c>
+      <c r="I37" s="125" t="n">
+        <v>4320</v>
+      </c>
+      <c r="J37" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K37" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L37" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M37" s="125" t="inlineStr"/>
+      <c r="N37" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/9</t>
+        </is>
+      </c>
+      <c r="O37" s="125" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="P37" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q37" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R37" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S37" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U37" s="125" t="inlineStr"/>
+      <c r="V37" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W37" s="125" t="inlineStr"/>
+      <c r="X37" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B38" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C38" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D38" s="125" t="inlineStr">
+        <is>
+          <t>6H1094B00</t>
+        </is>
+      </c>
+      <c r="E38" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F38" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G38" s="125" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H38" s="125" t="n">
+        <v>5350</v>
+      </c>
+      <c r="I38" s="125" t="n">
+        <v>5390</v>
+      </c>
+      <c r="J38" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K38" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L38" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M38" s="125" t="inlineStr"/>
+      <c r="N38" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="O38" s="125" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="P38" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q38" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R38" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S38" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U38" s="125" t="inlineStr"/>
+      <c r="V38" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W38" s="125" t="inlineStr"/>
+      <c r="X38" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B39" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C39" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D39" s="125" t="inlineStr">
+        <is>
+          <t>6H1094C00</t>
+        </is>
+      </c>
+      <c r="E39" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F39" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G39" s="125" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H39" s="125" t="n">
+        <v>5365</v>
+      </c>
+      <c r="I39" s="125" t="n">
+        <v>5405</v>
+      </c>
+      <c r="J39" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K39" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L39" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M39" s="125" t="inlineStr"/>
+      <c r="N39" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="O39" s="125" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="P39" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q39" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R39" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S39" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U39" s="125" t="inlineStr"/>
+      <c r="V39" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W39" s="125" t="inlineStr"/>
+      <c r="X39" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B40" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C40" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D40" s="125" t="inlineStr">
+        <is>
+          <t>6H1094D00</t>
+        </is>
+      </c>
+      <c r="E40" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F40" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G40" s="125" t="n">
+        <v>1155</v>
+      </c>
+      <c r="H40" s="125" t="n">
+        <v>5350</v>
+      </c>
+      <c r="I40" s="125" t="n">
+        <v>5390</v>
+      </c>
+      <c r="J40" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K40" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L40" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M40" s="125" t="inlineStr"/>
+      <c r="N40" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="O40" s="125" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="P40" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q40" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R40" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S40" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U40" s="125" t="inlineStr"/>
+      <c r="V40" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W40" s="125" t="inlineStr"/>
+      <c r="X40" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B41" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C41" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D41" s="125" t="inlineStr">
+        <is>
+          <t>6H1095A00</t>
+        </is>
+      </c>
+      <c r="E41" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F41" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G41" s="125" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H41" s="125" t="n">
+        <v>5415</v>
+      </c>
+      <c r="I41" s="125" t="n">
+        <v>5455</v>
+      </c>
+      <c r="J41" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K41" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L41" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M41" s="125" t="inlineStr"/>
+      <c r="N41" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="O41" s="125" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="P41" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q41" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R41" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S41" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U41" s="125" t="inlineStr"/>
+      <c r="V41" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W41" s="125" t="inlineStr"/>
+      <c r="X41" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B42" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C42" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D42" s="125" t="inlineStr">
+        <is>
+          <t>6H1095B00</t>
+        </is>
+      </c>
+      <c r="E42" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F42" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G42" s="125" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H42" s="125" t="n">
+        <v>5385</v>
+      </c>
+      <c r="I42" s="125" t="n">
+        <v>5425</v>
+      </c>
+      <c r="J42" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K42" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L42" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M42" s="125" t="inlineStr"/>
+      <c r="N42" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/10</t>
+        </is>
+      </c>
+      <c r="O42" s="125" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="P42" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q42" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R42" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S42" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U42" s="125" t="inlineStr"/>
+      <c r="V42" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W42" s="125" t="inlineStr"/>
+      <c r="X42" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B43" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C43" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D43" s="125" t="inlineStr">
+        <is>
+          <t>6H1095C00</t>
+        </is>
+      </c>
+      <c r="E43" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F43" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G43" s="125" t="n">
+        <v>1190</v>
+      </c>
+      <c r="H43" s="125" t="n">
+        <v>5585</v>
+      </c>
+      <c r="I43" s="125" t="n">
+        <v>5625</v>
+      </c>
+      <c r="J43" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K43" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L43" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M43" s="125" t="inlineStr"/>
+      <c r="N43" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="O43" s="125" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="P43" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q43" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R43" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S43" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U43" s="125" t="inlineStr"/>
+      <c r="V43" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W43" s="125" t="inlineStr"/>
+      <c r="X43" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B44" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C44" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D44" s="125" t="inlineStr">
+        <is>
+          <t>6H1096B00</t>
+        </is>
+      </c>
+      <c r="E44" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F44" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G44" s="125" t="n">
+        <v>1140</v>
+      </c>
+      <c r="H44" s="125" t="n">
+        <v>5290</v>
+      </c>
+      <c r="I44" s="125" t="n">
+        <v>5330</v>
+      </c>
+      <c r="J44" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K44" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L44" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M44" s="125" t="inlineStr"/>
+      <c r="N44" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="O44" s="125" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="P44" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q44" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R44" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S44" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U44" s="125" t="inlineStr"/>
+      <c r="V44" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W44" s="125" t="inlineStr"/>
+      <c r="X44" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B45" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C45" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D45" s="125" t="inlineStr">
+        <is>
+          <t>6H1096C00</t>
+        </is>
+      </c>
+      <c r="E45" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F45" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G45" s="125" t="n">
+        <v>1140</v>
+      </c>
+      <c r="H45" s="125" t="n">
+        <v>5305</v>
+      </c>
+      <c r="I45" s="125" t="n">
+        <v>5345</v>
+      </c>
+      <c r="J45" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K45" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L45" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M45" s="125" t="inlineStr"/>
+      <c r="N45" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="O45" s="125" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="P45" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q45" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R45" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S45" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U45" s="125" t="inlineStr"/>
+      <c r="V45" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W45" s="125" t="inlineStr"/>
+      <c r="X45" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B46" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C46" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D46" s="125" t="inlineStr">
+        <is>
+          <t>6H1097A00</t>
+        </is>
+      </c>
+      <c r="E46" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F46" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G46" s="125" t="n">
+        <v>1140</v>
+      </c>
+      <c r="H46" s="125" t="n">
+        <v>5315</v>
+      </c>
+      <c r="I46" s="125" t="n">
+        <v>5355</v>
+      </c>
+      <c r="J46" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K46" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L46" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M46" s="125" t="inlineStr"/>
+      <c r="N46" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="O46" s="125" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="P46" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q46" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R46" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S46" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U46" s="125" t="inlineStr"/>
+      <c r="V46" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W46" s="125" t="inlineStr"/>
+      <c r="X46" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B47" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C47" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D47" s="125" t="inlineStr">
+        <is>
+          <t>6H1098A00</t>
+        </is>
+      </c>
+      <c r="E47" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F47" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G47" s="125" t="n">
+        <v>1178</v>
+      </c>
+      <c r="H47" s="125" t="n">
+        <v>5500</v>
+      </c>
+      <c r="I47" s="125" t="n">
+        <v>5540</v>
+      </c>
+      <c r="J47" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K47" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L47" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M47" s="125" t="inlineStr"/>
+      <c r="N47" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="O47" s="125" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="P47" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q47" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R47" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S47" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U47" s="125" t="inlineStr"/>
+      <c r="V47" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W47" s="125" t="inlineStr"/>
+      <c r="X47" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B48" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C48" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D48" s="125" t="inlineStr">
+        <is>
+          <t>6H1098B00</t>
+        </is>
+      </c>
+      <c r="E48" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F48" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G48" s="125" t="n">
+        <v>1140</v>
+      </c>
+      <c r="H48" s="125" t="n">
+        <v>5305</v>
+      </c>
+      <c r="I48" s="125" t="n">
+        <v>5345</v>
+      </c>
+      <c r="J48" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K48" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L48" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M48" s="125" t="inlineStr"/>
+      <c r="N48" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="O48" s="125" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="P48" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q48" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R48" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S48" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U48" s="125" t="inlineStr"/>
+      <c r="V48" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W48" s="125" t="inlineStr"/>
+      <c r="X48" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B49" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C49" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D49" s="125" t="inlineStr">
+        <is>
+          <t>6H1098C00</t>
+        </is>
+      </c>
+      <c r="E49" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F49" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G49" s="125" t="n">
+        <v>1140</v>
+      </c>
+      <c r="H49" s="125" t="n">
+        <v>5310</v>
+      </c>
+      <c r="I49" s="125" t="n">
+        <v>5350</v>
+      </c>
+      <c r="J49" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K49" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L49" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M49" s="125" t="inlineStr"/>
+      <c r="N49" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="O49" s="125" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="P49" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q49" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R49" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S49" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U49" s="125" t="inlineStr"/>
+      <c r="V49" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W49" s="125" t="inlineStr"/>
+      <c r="X49" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B50" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C50" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D50" s="125" t="inlineStr">
+        <is>
+          <t>6H1098D00</t>
+        </is>
+      </c>
+      <c r="E50" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F50" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G50" s="125" t="n">
+        <v>1182</v>
+      </c>
+      <c r="H50" s="125" t="n">
+        <v>5465</v>
+      </c>
+      <c r="I50" s="125" t="n">
+        <v>5505</v>
+      </c>
+      <c r="J50" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K50" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L50" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M50" s="125" t="inlineStr"/>
+      <c r="N50" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="O50" s="125" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="P50" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q50" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R50" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S50" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U50" s="125" t="inlineStr"/>
+      <c r="V50" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W50" s="125" t="inlineStr"/>
+      <c r="X50" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B51" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C51" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D51" s="125" t="inlineStr">
+        <is>
+          <t>6H1099C00</t>
+        </is>
+      </c>
+      <c r="E51" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F51" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G51" s="125" t="n">
+        <v>1095</v>
+      </c>
+      <c r="H51" s="125" t="n">
+        <v>5105</v>
+      </c>
+      <c r="I51" s="125" t="n">
+        <v>5145</v>
+      </c>
+      <c r="J51" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K51" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L51" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M51" s="125" t="inlineStr"/>
+      <c r="N51" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="O51" s="125" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="P51" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q51" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R51" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S51" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U51" s="125" t="inlineStr"/>
+      <c r="V51" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W51" s="125" t="inlineStr"/>
+      <c r="X51" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B52" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C52" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D52" s="125" t="inlineStr">
+        <is>
+          <t>6H1099D00</t>
+        </is>
+      </c>
+      <c r="E52" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F52" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G52" s="125" t="n">
+        <v>1131</v>
+      </c>
+      <c r="H52" s="125" t="n">
+        <v>5240</v>
+      </c>
+      <c r="I52" s="125" t="n">
+        <v>5280</v>
+      </c>
+      <c r="J52" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K52" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L52" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M52" s="125" t="inlineStr"/>
+      <c r="N52" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="O52" s="125" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="P52" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q52" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R52" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S52" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U52" s="125" t="inlineStr"/>
+      <c r="V52" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W52" s="125" t="inlineStr"/>
+      <c r="X52" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B53" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C53" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D53" s="125" t="inlineStr">
+        <is>
+          <t>6H1100A00</t>
+        </is>
+      </c>
+      <c r="E53" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F53" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G53" s="125" t="n">
+        <v>1140</v>
+      </c>
+      <c r="H53" s="125" t="n">
+        <v>5350</v>
+      </c>
+      <c r="I53" s="125" t="n">
+        <v>5390</v>
+      </c>
+      <c r="J53" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K53" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L53" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M53" s="125" t="inlineStr"/>
+      <c r="N53" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="O53" s="125" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="P53" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q53" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R53" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S53" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U53" s="125" t="inlineStr"/>
+      <c r="V53" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W53" s="125" t="inlineStr"/>
+      <c r="X53" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B54" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C54" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D54" s="125" t="inlineStr">
+        <is>
+          <t>6H1100B00</t>
+        </is>
+      </c>
+      <c r="E54" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F54" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G54" s="125" t="n">
+        <v>1140</v>
+      </c>
+      <c r="H54" s="125" t="n">
+        <v>5320</v>
+      </c>
+      <c r="I54" s="125" t="n">
+        <v>5360</v>
+      </c>
+      <c r="J54" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K54" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L54" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M54" s="125" t="inlineStr"/>
+      <c r="N54" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="O54" s="125" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="P54" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q54" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R54" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S54" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U54" s="125" t="inlineStr"/>
+      <c r="V54" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W54" s="125" t="inlineStr"/>
+      <c r="X54" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B55" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C55" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D55" s="125" t="inlineStr">
+        <is>
+          <t>6H1100C00</t>
+        </is>
+      </c>
+      <c r="E55" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F55" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G55" s="125" t="n">
+        <v>1140</v>
+      </c>
+      <c r="H55" s="125" t="n">
+        <v>5320</v>
+      </c>
+      <c r="I55" s="125" t="n">
+        <v>5360</v>
+      </c>
+      <c r="J55" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K55" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L55" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M55" s="125" t="inlineStr"/>
+      <c r="N55" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="O55" s="125" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="P55" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q55" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R55" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S55" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U55" s="125" t="inlineStr"/>
+      <c r="V55" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W55" s="125" t="inlineStr"/>
+      <c r="X55" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B56" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C56" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D56" s="125" t="inlineStr">
+        <is>
+          <t>6H1100D00</t>
+        </is>
+      </c>
+      <c r="E56" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F56" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G56" s="125" t="n">
+        <v>1134</v>
+      </c>
+      <c r="H56" s="125" t="n">
+        <v>5255</v>
+      </c>
+      <c r="I56" s="125" t="n">
+        <v>5295</v>
+      </c>
+      <c r="J56" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K56" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L56" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M56" s="125" t="inlineStr"/>
+      <c r="N56" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="O56" s="125" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="P56" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q56" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R56" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S56" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U56" s="125" t="inlineStr"/>
+      <c r="V56" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W56" s="125" t="inlineStr"/>
+      <c r="X56" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B57" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C57" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D57" s="125" t="inlineStr">
+        <is>
+          <t>6H1101A00</t>
+        </is>
+      </c>
+      <c r="E57" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F57" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G57" s="125" t="n">
+        <v>1140</v>
+      </c>
+      <c r="H57" s="125" t="n">
+        <v>5340</v>
+      </c>
+      <c r="I57" s="125" t="n">
+        <v>5380</v>
+      </c>
+      <c r="J57" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K57" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L57" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M57" s="125" t="inlineStr"/>
+      <c r="N57" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="O57" s="125" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="P57" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q57" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R57" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S57" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U57" s="125" t="inlineStr"/>
+      <c r="V57" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W57" s="125" t="inlineStr"/>
+      <c r="X57" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B58" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C58" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D58" s="125" t="inlineStr">
+        <is>
+          <t>6H1101B00</t>
+        </is>
+      </c>
+      <c r="E58" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F58" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G58" s="125" t="n">
+        <v>1140</v>
+      </c>
+      <c r="H58" s="125" t="n">
+        <v>5320</v>
+      </c>
+      <c r="I58" s="125" t="n">
+        <v>5360</v>
+      </c>
+      <c r="J58" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K58" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L58" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M58" s="125" t="inlineStr"/>
+      <c r="N58" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="O58" s="125" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="P58" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q58" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R58" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S58" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U58" s="125" t="inlineStr"/>
+      <c r="V58" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W58" s="125" t="inlineStr"/>
+      <c r="X58" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B59" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C59" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D59" s="125" t="inlineStr">
+        <is>
+          <t>6H1101C00</t>
+        </is>
+      </c>
+      <c r="E59" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F59" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G59" s="125" t="n">
+        <v>1140</v>
+      </c>
+      <c r="H59" s="125" t="n">
+        <v>5315</v>
+      </c>
+      <c r="I59" s="125" t="n">
+        <v>5355</v>
+      </c>
+      <c r="J59" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K59" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L59" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M59" s="125" t="inlineStr"/>
+      <c r="N59" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="O59" s="125" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="P59" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q59" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R59" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S59" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U59" s="125" t="inlineStr"/>
+      <c r="V59" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W59" s="125" t="inlineStr"/>
+      <c r="X59" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B60" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C60" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D60" s="125" t="inlineStr">
+        <is>
+          <t>6H1101D00</t>
+        </is>
+      </c>
+      <c r="E60" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F60" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G60" s="125" t="n">
+        <v>1198</v>
+      </c>
+      <c r="H60" s="125" t="n">
+        <v>5540</v>
+      </c>
+      <c r="I60" s="125" t="n">
+        <v>5580</v>
+      </c>
+      <c r="J60" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K60" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L60" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M60" s="125" t="inlineStr"/>
+      <c r="N60" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="O60" s="125" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="P60" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q60" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R60" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S60" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U60" s="125" t="inlineStr"/>
+      <c r="V60" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W60" s="125" t="inlineStr"/>
+      <c r="X60" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B61" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C61" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D61" s="125" t="inlineStr">
+        <is>
+          <t>6H1102A00</t>
+        </is>
+      </c>
+      <c r="E61" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F61" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G61" s="125" t="n">
+        <v>1140</v>
+      </c>
+      <c r="H61" s="125" t="n">
+        <v>5340</v>
+      </c>
+      <c r="I61" s="125" t="n">
+        <v>5380</v>
+      </c>
+      <c r="J61" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K61" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L61" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M61" s="125" t="inlineStr"/>
+      <c r="N61" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="O61" s="125" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="P61" s="125" t="n">
+        <v>1202</v>
+      </c>
+      <c r="Q61" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R61" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S61" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U61" s="125" t="inlineStr"/>
+      <c r="V61" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W61" s="125" t="inlineStr"/>
+      <c r="X61" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B62" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C62" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D62" s="125" t="inlineStr">
+        <is>
+          <t>6H1102B00</t>
+        </is>
+      </c>
+      <c r="E62" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F62" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G62" s="125" t="n">
+        <v>1140</v>
+      </c>
+      <c r="H62" s="125" t="n">
+        <v>5300</v>
+      </c>
+      <c r="I62" s="125" t="n">
+        <v>5340</v>
+      </c>
+      <c r="J62" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K62" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L62" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M62" s="125" t="inlineStr"/>
+      <c r="N62" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="O62" s="125" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="P62" s="125" t="n">
+        <v>1202</v>
+      </c>
+      <c r="Q62" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R62" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S62" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U62" s="125" t="inlineStr"/>
+      <c r="V62" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W62" s="125" t="inlineStr"/>
+      <c r="X62" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B63" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C63" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D63" s="125" t="inlineStr">
+        <is>
+          <t>6H1102C00</t>
+        </is>
+      </c>
+      <c r="E63" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F63" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G63" s="125" t="n">
+        <v>1140</v>
+      </c>
+      <c r="H63" s="125" t="n">
+        <v>5305</v>
+      </c>
+      <c r="I63" s="125" t="n">
+        <v>5345</v>
+      </c>
+      <c r="J63" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K63" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L63" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M63" s="125" t="inlineStr"/>
+      <c r="N63" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="O63" s="125" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="P63" s="125" t="n">
+        <v>1202</v>
+      </c>
+      <c r="Q63" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R63" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S63" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U63" s="125" t="inlineStr"/>
+      <c r="V63" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W63" s="125" t="inlineStr"/>
+      <c r="X63" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B64" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C64" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D64" s="125" t="inlineStr">
+        <is>
+          <t>6H1102D00</t>
+        </is>
+      </c>
+      <c r="E64" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F64" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G64" s="125" t="n">
+        <v>1208</v>
+      </c>
+      <c r="H64" s="125" t="n">
+        <v>5580</v>
+      </c>
+      <c r="I64" s="125" t="n">
+        <v>5620</v>
+      </c>
+      <c r="J64" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K64" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L64" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M64" s="125" t="inlineStr"/>
+      <c r="N64" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="O64" s="125" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="P64" s="125" t="n">
+        <v>1202</v>
+      </c>
+      <c r="Q64" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R64" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S64" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U64" s="125" t="inlineStr"/>
+      <c r="V64" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W64" s="125" t="inlineStr"/>
+      <c r="X64" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B65" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C65" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D65" s="125" t="inlineStr">
+        <is>
+          <t>6H1103A00</t>
+        </is>
+      </c>
+      <c r="E65" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F65" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G65" s="125" t="n">
+        <v>1140</v>
+      </c>
+      <c r="H65" s="125" t="n">
+        <v>5325</v>
+      </c>
+      <c r="I65" s="125" t="n">
+        <v>5365</v>
+      </c>
+      <c r="J65" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K65" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L65" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M65" s="125" t="inlineStr"/>
+      <c r="N65" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="O65" s="125" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="P65" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q65" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R65" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S65" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U65" s="125" t="inlineStr"/>
+      <c r="V65" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W65" s="125" t="inlineStr"/>
+      <c r="X65" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B66" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C66" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D66" s="125" t="inlineStr">
+        <is>
+          <t>6H1103B00</t>
+        </is>
+      </c>
+      <c r="E66" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F66" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G66" s="125" t="n">
+        <v>1140</v>
+      </c>
+      <c r="H66" s="125" t="n">
+        <v>5305</v>
+      </c>
+      <c r="I66" s="125" t="n">
+        <v>5345</v>
+      </c>
+      <c r="J66" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K66" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L66" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M66" s="125" t="inlineStr"/>
+      <c r="N66" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="O66" s="125" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="P66" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q66" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R66" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S66" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U66" s="125" t="inlineStr"/>
+      <c r="V66" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W66" s="125" t="inlineStr"/>
+      <c r="X66" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B67" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C67" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D67" s="125" t="inlineStr">
+        <is>
+          <t>6H1103C00</t>
+        </is>
+      </c>
+      <c r="E67" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F67" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G67" s="125" t="n">
+        <v>1140</v>
+      </c>
+      <c r="H67" s="125" t="n">
+        <v>5310</v>
+      </c>
+      <c r="I67" s="125" t="n">
+        <v>5350</v>
+      </c>
+      <c r="J67" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K67" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L67" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M67" s="125" t="inlineStr"/>
+      <c r="N67" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="O67" s="125" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="P67" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q67" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R67" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S67" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U67" s="125" t="inlineStr"/>
+      <c r="V67" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W67" s="125" t="inlineStr"/>
+      <c r="X67" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B68" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C68" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D68" s="125" t="inlineStr">
+        <is>
+          <t>6H1103D00</t>
+        </is>
+      </c>
+      <c r="E68" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F68" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G68" s="125" t="n">
+        <v>1213</v>
+      </c>
+      <c r="H68" s="125" t="n">
+        <v>5605</v>
+      </c>
+      <c r="I68" s="125" t="n">
+        <v>5645</v>
+      </c>
+      <c r="J68" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K68" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L68" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M68" s="125" t="inlineStr"/>
+      <c r="N68" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="O68" s="125" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="P68" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q68" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R68" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S68" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U68" s="125" t="inlineStr"/>
+      <c r="V68" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W68" s="125" t="inlineStr"/>
+      <c r="X68" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B69" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C69" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D69" s="125" t="inlineStr">
+        <is>
+          <t>6H1104A00</t>
+        </is>
+      </c>
+      <c r="E69" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F69" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G69" s="125" t="n">
+        <v>1140</v>
+      </c>
+      <c r="H69" s="125" t="n">
+        <v>5335</v>
+      </c>
+      <c r="I69" s="125" t="n">
+        <v>5375</v>
+      </c>
+      <c r="J69" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K69" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L69" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M69" s="125" t="inlineStr"/>
+      <c r="N69" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="O69" s="125" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="P69" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q69" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R69" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S69" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U69" s="125" t="inlineStr"/>
+      <c r="V69" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W69" s="125" t="inlineStr"/>
+      <c r="X69" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B70" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C70" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D70" s="125" t="inlineStr">
+        <is>
+          <t>6H1104B00</t>
+        </is>
+      </c>
+      <c r="E70" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F70" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G70" s="125" t="n">
+        <v>1140</v>
+      </c>
+      <c r="H70" s="125" t="n">
+        <v>5305</v>
+      </c>
+      <c r="I70" s="125" t="n">
+        <v>5345</v>
+      </c>
+      <c r="J70" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K70" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L70" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M70" s="125" t="inlineStr"/>
+      <c r="N70" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="O70" s="125" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="P70" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q70" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R70" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S70" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U70" s="125" t="inlineStr"/>
+      <c r="V70" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W70" s="125" t="inlineStr"/>
+      <c r="X70" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B71" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C71" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D71" s="125" t="inlineStr">
+        <is>
+          <t>6H1104C00</t>
+        </is>
+      </c>
+      <c r="E71" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F71" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G71" s="125" t="n">
+        <v>1140</v>
+      </c>
+      <c r="H71" s="125" t="n">
+        <v>5315</v>
+      </c>
+      <c r="I71" s="125" t="n">
+        <v>5355</v>
+      </c>
+      <c r="J71" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K71" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L71" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M71" s="125" t="inlineStr"/>
+      <c r="N71" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="O71" s="125" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="P71" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q71" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R71" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S71" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U71" s="125" t="inlineStr"/>
+      <c r="V71" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W71" s="125" t="inlineStr"/>
+      <c r="X71" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B72" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C72" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D72" s="125" t="inlineStr">
+        <is>
+          <t>6H1104D00</t>
+        </is>
+      </c>
+      <c r="E72" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F72" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G72" s="125" t="n">
+        <v>1189</v>
+      </c>
+      <c r="H72" s="125" t="n">
+        <v>5500</v>
+      </c>
+      <c r="I72" s="125" t="n">
+        <v>5540</v>
+      </c>
+      <c r="J72" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K72" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L72" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M72" s="125" t="inlineStr"/>
+      <c r="N72" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="O72" s="125" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="P72" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q72" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R72" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S72" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U72" s="125" t="inlineStr"/>
+      <c r="V72" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W72" s="125" t="inlineStr"/>
+      <c r="X72" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B73" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C73" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D73" s="125" t="inlineStr">
+        <is>
+          <t>6H1105A00</t>
+        </is>
+      </c>
+      <c r="E73" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F73" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G73" s="125" t="n">
+        <v>1140</v>
+      </c>
+      <c r="H73" s="125" t="n">
+        <v>5340</v>
+      </c>
+      <c r="I73" s="125" t="n">
+        <v>5380</v>
+      </c>
+      <c r="J73" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K73" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L73" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M73" s="125" t="inlineStr"/>
+      <c r="N73" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="O73" s="125" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="P73" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q73" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R73" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S73" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U73" s="125" t="inlineStr"/>
+      <c r="V73" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W73" s="125" t="inlineStr"/>
+      <c r="X73" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B74" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C74" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D74" s="125" t="inlineStr">
+        <is>
+          <t>6H1105B00</t>
+        </is>
+      </c>
+      <c r="E74" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F74" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G74" s="125" t="n">
+        <v>1140</v>
+      </c>
+      <c r="H74" s="125" t="n">
+        <v>5300</v>
+      </c>
+      <c r="I74" s="125" t="n">
+        <v>5340</v>
+      </c>
+      <c r="J74" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K74" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L74" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M74" s="125" t="inlineStr"/>
+      <c r="N74" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="O74" s="125" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="P74" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q74" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R74" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S74" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U74" s="125" t="inlineStr"/>
+      <c r="V74" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W74" s="125" t="inlineStr"/>
+      <c r="X74" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B75" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C75" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D75" s="125" t="inlineStr">
+        <is>
+          <t>6H1105C00</t>
+        </is>
+      </c>
+      <c r="E75" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F75" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G75" s="125" t="n">
+        <v>1140</v>
+      </c>
+      <c r="H75" s="125" t="n">
+        <v>5315</v>
+      </c>
+      <c r="I75" s="125" t="n">
+        <v>5355</v>
+      </c>
+      <c r="J75" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K75" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L75" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M75" s="125" t="inlineStr"/>
+      <c r="N75" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="O75" s="125" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="P75" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q75" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R75" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S75" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U75" s="125" t="inlineStr"/>
+      <c r="V75" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W75" s="125" t="inlineStr"/>
+      <c r="X75" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="125" t="inlineStr">
+        <is>
+          <t>2026/4/24</t>
+        </is>
+      </c>
+      <c r="B76" s="125" t="inlineStr">
+        <is>
+          <t>冰岚+杭州宝晟</t>
+        </is>
+      </c>
+      <c r="C76" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2J003</t>
+        </is>
+      </c>
+      <c r="D76" s="125" t="inlineStr">
+        <is>
+          <t>6H1106A00</t>
+        </is>
+      </c>
+      <c r="E76" s="125" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F76" s="125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G76" s="125" t="n">
+        <v>1140</v>
+      </c>
+      <c r="H76" s="125" t="n">
+        <v>5335</v>
+      </c>
+      <c r="I76" s="125" t="n">
+        <v>5375</v>
+      </c>
+      <c r="J76" s="125" t="inlineStr">
+        <is>
+          <t>AZ200</t>
+        </is>
+      </c>
+      <c r="K76" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L76" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M76" s="125" t="inlineStr"/>
+      <c r="N76" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
+      <c r="O76" s="125" t="n">
+        <v>0.536</v>
+      </c>
+      <c r="P76" s="125" t="n">
+        <v>1203</v>
+      </c>
+      <c r="Q76" s="125" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R76" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S76" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" s="125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U76" s="125" t="inlineStr"/>
+      <c r="V76" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W76" s="125" t="inlineStr"/>
+      <c r="X76" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23787,7 +28978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X31"/>
+  <dimension ref="A1:X32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25388,97 +30579,101 @@
       <c r="W18" s="123" t="n"/>
       <c r="X18" s="123" t="n"/>
     </row>
-    <row r="20">
-      <c r="A20" s="123" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="125" t="inlineStr">
         <is>
           <t>2026/4/20</t>
         </is>
       </c>
-      <c r="B20" s="123" t="inlineStr">
+      <c r="B19" s="125" t="inlineStr">
         <is>
           <t>贻裕</t>
         </is>
       </c>
-      <c r="C20" s="123" t="inlineStr">
-        <is>
-          <t>L3GS2A208</t>
-        </is>
-      </c>
-      <c r="D20" s="123" t="inlineStr">
-        <is>
-          <t>6HL146A00</t>
-        </is>
-      </c>
-      <c r="E20" s="123" t="n">
+      <c r="C19" s="125" t="inlineStr">
+        <is>
+          <t>L3GS2A207</t>
+        </is>
+      </c>
+      <c r="D19" s="125" t="inlineStr">
+        <is>
+          <t>6HL759D00</t>
+        </is>
+      </c>
+      <c r="E19" s="125" t="n">
         <v>2.95</v>
       </c>
-      <c r="F20" s="123" t="n">
-        <v>1175</v>
-      </c>
-      <c r="G20" s="123" t="n">
-        <v>281</v>
-      </c>
-      <c r="H20" s="123" t="n">
-        <v>7700</v>
-      </c>
-      <c r="I20" s="123" t="n">
-        <v>7740</v>
-      </c>
-      <c r="J20" s="123" t="inlineStr">
+      <c r="F19" s="125" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G19" s="125" t="n">
+        <v>263</v>
+      </c>
+      <c r="H19" s="125" t="n">
+        <v>6080</v>
+      </c>
+      <c r="I19" s="125" t="n">
+        <v>6120</v>
+      </c>
+      <c r="J19" s="125" t="inlineStr">
         <is>
           <t>Z120</t>
         </is>
       </c>
-      <c r="K20" s="123" t="inlineStr">
-        <is>
-          <t>_</t>
-        </is>
-      </c>
-      <c r="L20" s="123" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="M20" s="123" t="n"/>
-      <c r="N20" s="123" t="inlineStr">
-        <is>
-          <t>2026/5/4</t>
-        </is>
-      </c>
-      <c r="O20" s="123" t="n">
-        <v>2.955</v>
-      </c>
-      <c r="P20" s="123" t="n">
-        <v>1179</v>
-      </c>
-      <c r="Q20" s="123" t="inlineStr">
+      <c r="K19" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L19" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M19" s="125" t="inlineStr"/>
+      <c r="N19" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/10</t>
+        </is>
+      </c>
+      <c r="O19" s="125" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="P19" s="125" t="n">
+        <v>1002</v>
+      </c>
+      <c r="Q19" s="125" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
       </c>
-      <c r="R20" s="123" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="S20" s="123" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T20" s="123" t="inlineStr">
+      <c r="R19" s="125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="S19" s="125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" s="125" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="U20" s="123" t="n"/>
-      <c r="V20" s="123" t="inlineStr">
-        <is>
-          <t>_</t>
-        </is>
-      </c>
-      <c r="W20" s="123" t="n"/>
-      <c r="X20" s="123" t="n"/>
+      <c r="U19" s="125" t="inlineStr"/>
+      <c r="V19" s="125" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W19" s="125" t="inlineStr"/>
+      <c r="X19" s="125" t="inlineStr">
+        <is>
+          <t>2026/5/11</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="123" t="inlineStr">
@@ -25498,7 +30693,7 @@
       </c>
       <c r="D21" s="123" t="inlineStr">
         <is>
-          <t>6HL146B00</t>
+          <t>6HL146A00</t>
         </is>
       </c>
       <c r="E21" s="123" t="n">
@@ -25508,13 +30703,13 @@
         <v>1175</v>
       </c>
       <c r="G21" s="123" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H21" s="123" t="n">
-        <v>7730</v>
+        <v>7700</v>
       </c>
       <c r="I21" s="123" t="n">
-        <v>7770</v>
+        <v>7740</v>
       </c>
       <c r="J21" s="123" t="inlineStr">
         <is>
@@ -25590,7 +30785,7 @@
       </c>
       <c r="D22" s="123" t="inlineStr">
         <is>
-          <t>6HL146C00</t>
+          <t>6HL146B00</t>
         </is>
       </c>
       <c r="E22" s="123" t="n">
@@ -25600,13 +30795,13 @@
         <v>1175</v>
       </c>
       <c r="G22" s="123" t="n">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="H22" s="123" t="n">
-        <v>7860</v>
+        <v>7730</v>
       </c>
       <c r="I22" s="123" t="n">
-        <v>7900</v>
+        <v>7770</v>
       </c>
       <c r="J22" s="123" t="inlineStr">
         <is>
@@ -25682,7 +30877,7 @@
       </c>
       <c r="D23" s="123" t="inlineStr">
         <is>
-          <t>6HL147A00</t>
+          <t>6HL146C00</t>
         </is>
       </c>
       <c r="E23" s="123" t="n">
@@ -25692,13 +30887,13 @@
         <v>1175</v>
       </c>
       <c r="G23" s="123" t="n">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="H23" s="123" t="n">
-        <v>7305</v>
+        <v>7860</v>
       </c>
       <c r="I23" s="123" t="n">
-        <v>7345</v>
+        <v>7900</v>
       </c>
       <c r="J23" s="123" t="inlineStr">
         <is>
@@ -25774,7 +30969,7 @@
       </c>
       <c r="D24" s="123" t="inlineStr">
         <is>
-          <t>6HL147B00</t>
+          <t>6HL147A00</t>
         </is>
       </c>
       <c r="E24" s="123" t="n">
@@ -25784,13 +30979,13 @@
         <v>1175</v>
       </c>
       <c r="G24" s="123" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H24" s="123" t="n">
-        <v>7295</v>
+        <v>7305</v>
       </c>
       <c r="I24" s="123" t="n">
-        <v>7335</v>
+        <v>7345</v>
       </c>
       <c r="J24" s="123" t="inlineStr">
         <is>
@@ -25866,7 +31061,7 @@
       </c>
       <c r="D25" s="123" t="inlineStr">
         <is>
-          <t>6HL147C00</t>
+          <t>6HL147B00</t>
         </is>
       </c>
       <c r="E25" s="123" t="n">
@@ -25876,13 +31071,13 @@
         <v>1175</v>
       </c>
       <c r="G25" s="123" t="n">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="H25" s="123" t="n">
-        <v>7480</v>
+        <v>7295</v>
       </c>
       <c r="I25" s="123" t="n">
-        <v>7520</v>
+        <v>7335</v>
       </c>
       <c r="J25" s="123" t="inlineStr">
         <is>
@@ -25958,7 +31153,7 @@
       </c>
       <c r="D26" s="123" t="inlineStr">
         <is>
-          <t>6HL148A00</t>
+          <t>6HL147C00</t>
         </is>
       </c>
       <c r="E26" s="123" t="n">
@@ -25968,13 +31163,13 @@
         <v>1175</v>
       </c>
       <c r="G26" s="123" t="n">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="H26" s="123" t="n">
-        <v>7285</v>
+        <v>7480</v>
       </c>
       <c r="I26" s="123" t="n">
-        <v>7325</v>
+        <v>7520</v>
       </c>
       <c r="J26" s="123" t="inlineStr">
         <is>
@@ -25998,7 +31193,7 @@
         </is>
       </c>
       <c r="O26" s="123" t="n">
-        <v>2.953</v>
+        <v>2.955</v>
       </c>
       <c r="P26" s="123" t="n">
         <v>1179</v>
@@ -26050,7 +31245,7 @@
       </c>
       <c r="D27" s="123" t="inlineStr">
         <is>
-          <t>6HL148B00</t>
+          <t>6HL148A00</t>
         </is>
       </c>
       <c r="E27" s="123" t="n">
@@ -26060,13 +31255,13 @@
         <v>1175</v>
       </c>
       <c r="G27" s="123" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H27" s="123" t="n">
-        <v>7310</v>
+        <v>7285</v>
       </c>
       <c r="I27" s="123" t="n">
-        <v>7350</v>
+        <v>7325</v>
       </c>
       <c r="J27" s="123" t="inlineStr">
         <is>
@@ -26142,7 +31337,7 @@
       </c>
       <c r="D28" s="123" t="inlineStr">
         <is>
-          <t>6HL148C00</t>
+          <t>6HL148B00</t>
         </is>
       </c>
       <c r="E28" s="123" t="n">
@@ -26152,13 +31347,13 @@
         <v>1175</v>
       </c>
       <c r="G28" s="123" t="n">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="H28" s="123" t="n">
-        <v>7565</v>
+        <v>7310</v>
       </c>
       <c r="I28" s="123" t="n">
-        <v>7605</v>
+        <v>7350</v>
       </c>
       <c r="J28" s="123" t="inlineStr">
         <is>
@@ -26178,7 +31373,7 @@
       <c r="M28" s="123" t="n"/>
       <c r="N28" s="123" t="inlineStr">
         <is>
-          <t>2026/5/3</t>
+          <t>2026/5/4</t>
         </is>
       </c>
       <c r="O28" s="123" t="n">
@@ -26234,7 +31429,7 @@
       </c>
       <c r="D29" s="123" t="inlineStr">
         <is>
-          <t>6HL149A00</t>
+          <t>6HL148C00</t>
         </is>
       </c>
       <c r="E29" s="123" t="n">
@@ -26244,13 +31439,13 @@
         <v>1175</v>
       </c>
       <c r="G29" s="123" t="n">
-        <v>253</v>
+        <v>276</v>
       </c>
       <c r="H29" s="123" t="n">
-        <v>6920</v>
+        <v>7565</v>
       </c>
       <c r="I29" s="123" t="n">
-        <v>6960</v>
+        <v>7605</v>
       </c>
       <c r="J29" s="123" t="inlineStr">
         <is>
@@ -26274,7 +31469,7 @@
         </is>
       </c>
       <c r="O29" s="123" t="n">
-        <v>2.95</v>
+        <v>2.953</v>
       </c>
       <c r="P29" s="123" t="n">
         <v>1179</v>
@@ -26326,7 +31521,7 @@
       </c>
       <c r="D30" s="123" t="inlineStr">
         <is>
-          <t>6HL149B00</t>
+          <t>6HL149A00</t>
         </is>
       </c>
       <c r="E30" s="123" t="n">
@@ -26336,13 +31531,13 @@
         <v>1175</v>
       </c>
       <c r="G30" s="123" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H30" s="123" t="n">
-        <v>6900</v>
+        <v>6920</v>
       </c>
       <c r="I30" s="123" t="n">
-        <v>6940</v>
+        <v>6960</v>
       </c>
       <c r="J30" s="123" t="inlineStr">
         <is>
@@ -26418,7 +31613,7 @@
       </c>
       <c r="D31" s="123" t="inlineStr">
         <is>
-          <t>6HL149C00</t>
+          <t>6HL149B00</t>
         </is>
       </c>
       <c r="E31" s="123" t="n">
@@ -26428,13 +31623,13 @@
         <v>1175</v>
       </c>
       <c r="G31" s="123" t="n">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="H31" s="123" t="n">
-        <v>6745</v>
+        <v>6900</v>
       </c>
       <c r="I31" s="123" t="n">
-        <v>6785</v>
+        <v>6940</v>
       </c>
       <c r="J31" s="123" t="inlineStr">
         <is>
@@ -26491,6 +31686,98 @@
       </c>
       <c r="W31" s="123" t="n"/>
       <c r="X31" s="123" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="123" t="inlineStr">
+        <is>
+          <t>2026/4/20</t>
+        </is>
+      </c>
+      <c r="B32" s="123" t="inlineStr">
+        <is>
+          <t>贻裕</t>
+        </is>
+      </c>
+      <c r="C32" s="123" t="inlineStr">
+        <is>
+          <t>L3GS2A208</t>
+        </is>
+      </c>
+      <c r="D32" s="123" t="inlineStr">
+        <is>
+          <t>6HL149C00</t>
+        </is>
+      </c>
+      <c r="E32" s="123" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="F32" s="123" t="n">
+        <v>1175</v>
+      </c>
+      <c r="G32" s="123" t="n">
+        <v>246</v>
+      </c>
+      <c r="H32" s="123" t="n">
+        <v>6745</v>
+      </c>
+      <c r="I32" s="123" t="n">
+        <v>6785</v>
+      </c>
+      <c r="J32" s="123" t="inlineStr">
+        <is>
+          <t>Z120</t>
+        </is>
+      </c>
+      <c r="K32" s="123" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L32" s="123" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="M32" s="123" t="n"/>
+      <c r="N32" s="123" t="inlineStr">
+        <is>
+          <t>2026/5/3</t>
+        </is>
+      </c>
+      <c r="O32" s="123" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P32" s="123" t="n">
+        <v>1179</v>
+      </c>
+      <c r="Q32" s="123" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="R32" s="123" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="S32" s="123" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" s="123" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="U32" s="123" t="n"/>
+      <c r="V32" s="123" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="W32" s="123" t="n"/>
+      <c r="X32" s="123" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
